--- a/TestData/Group07_DataFetching.xlsx
+++ b/TestData/Group07_DataFetching.xlsx
@@ -1,37 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{718DBC6D-E19C-4DEF-9374-3C82434953B2}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Testing\OneDrive - TestingXperts Private Limited\Documents\UiPath Project Potfolio\AwwardsTestingLibrary\TestData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="dhruv" sheetId="1" r:id="rId1"/>
+    <sheet name="nihar" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>No.</t>
   </si>
@@ -58,12 +46,30 @@
   </si>
   <si>
     <t>site.......</t>
+  </si>
+  <si>
+    <t>DevName</t>
+  </si>
+  <si>
+    <t>NomineeName</t>
+  </si>
+  <si>
+    <t>Louis Paquet</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>27b</t>
+  </si>
+  <si>
+    <t>ToyFight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -77,7 +83,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -90,13 +95,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -109,19 +108,11 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -130,10 +121,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -302,6 +293,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -328,24 +320,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -406,30 +399,23 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.542969" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.45313" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45.75">
+    <row r="2" ht="58">
       <c r="A2">
         <v>1</v>
       </c>
@@ -465,8 +451,43 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{7FADD03B-9A32-4A91-A91A-8560E8B05189}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="15.63281" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>
--- a/TestData/Group07_DataFetching.xlsx
+++ b/TestData/Group07_DataFetching.xlsx
@@ -1,37 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{718DBC6D-E19C-4DEF-9374-3C82434953B2}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Testing\OneDrive - TestingXperts Private Limited\Documents\UiPath\AwwardsTestingLibrary\TestData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="dhruv" sheetId="1" r:id="rId1"/>
+    <sheet name="aradhika" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>No.</t>
   </si>
@@ -58,12 +46,42 @@
   </si>
   <si>
     <t>site.......</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>Job_name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>Jobs</t>
+  </si>
+  <si>
+    <t>Senior Designer (UX/UI Websites)</t>
+  </si>
+  <si>
+    <t>Programming</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -77,7 +95,6 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -90,13 +107,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -109,19 +120,11 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -130,10 +133,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -302,6 +305,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -328,24 +332,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -406,30 +411,23 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.570313" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45.75">
+    <row r="2" ht="60">
       <c r="A2">
         <v>1</v>
       </c>
@@ -465,8 +463,54 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{7FADD03B-9A32-4A91-A91A-8560E8B05189}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20.28516" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85547" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>
--- a/TestData/Group07_DataFetching.xlsx
+++ b/TestData/Group07_DataFetching.xlsx
@@ -1,25 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Testing\Documents\AwwardsTestingLibrary\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FB90811-7CC8-42AF-BE11-62E409E3A975}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dhruv" sheetId="1" r:id="rId1"/>
-    <sheet name="gurneet" sheetId="2" r:id="rId2"/>
+    <sheet name="nihar" sheetId="4" r:id="rId2"/>
+    <sheet name="Gurneet" sheetId="6" r:id="rId3"/>
+    <sheet name="aradhika" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>No.</t>
   </si>
@@ -27,27 +42,45 @@
     <t>username</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>Password</t>
   </si>
   <si>
     <t>search</t>
   </si>
   <si>
-    <t>dhruv</t>
-  </si>
-  <si>
-    <t>dhruvairan08@gmail.comn</t>
-  </si>
-  <si>
-    <t>Dhruv@123#</t>
+    <t>Cynthia_Clawhauser</t>
+  </si>
+  <si>
+    <t>Testing@123</t>
   </si>
   <si>
     <t>site.......</t>
   </si>
   <si>
+    <t>DevName</t>
+  </si>
+  <si>
+    <t>NomineeName</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Louis Paquet</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>#B42625</t>
+  </si>
+  <si>
+    <t>Social Responsibility</t>
+  </si>
+  <si>
     <t>Company Name</t>
   </si>
   <si>
@@ -118,13 +151,46 @@
   </si>
   <si>
     <t>Select Professional</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>Job_name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Senior Designer (UX/UI Websites)</t>
+  </si>
+  <si>
+    <t>Programming</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Jobs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,37 +203,65 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -176,10 +270,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -348,7 +442,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -375,25 +468,24 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -454,23 +546,30 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="9.570313" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,139 +582,233 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="60">
+    </row>
+    <row r="2" spans="1:4" ht="30.75">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43CB91A1-D528-4E47-B4F0-AC30B883B339}">
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="23.85547" customWidth="1"/>
-    <col min="3" max="3" width="12.57031" customWidth="1"/>
-    <col min="4" max="4" width="14.28516" customWidth="1"/>
-    <col min="9" max="9" width="27.28516" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.855469" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.85547" customWidth="1"/>
-    <col min="15" max="15" width="17.71094" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFDF6DB-F956-48D7-9C21-826376965665}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2">
+        <v>458798745</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="2">
+        <v>160017</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="3">
+        <v>46368</v>
+      </c>
+      <c r="K2" s="2">
+        <v>123</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1EAF14C-25F3-4773-A325-EFB2BD29F8CC}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1"/>
-    </row>
-    <row r="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
-        <v>458798745</v>
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2">
-        <v>160017</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="2">
-        <v>46368</v>
-      </c>
-      <c r="K2">
-        <v>123</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>